--- a/res.xlsx
+++ b/res.xlsx
@@ -1647,9 +1647,13 @@
         <v>0</v>
       </c>
       <c r="I7" s="27" t="n"/>
-      <c r="J7" s="26" t="n"/>
+      <c r="J7" s="26" t="n">
+        <v>172</v>
+      </c>
       <c r="K7" s="27" t="n"/>
-      <c r="L7" s="26" t="n"/>
+      <c r="L7" s="26" t="n">
+        <v>213</v>
+      </c>
       <c r="M7" s="27" t="n"/>
       <c r="N7" s="26" t="n"/>
       <c r="O7" s="27" t="n"/>
@@ -1764,9 +1768,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="27" t="n"/>
-      <c r="J8" s="26" t="n"/>
+      <c r="J8" s="26" t="n">
+        <v>172</v>
+      </c>
       <c r="K8" s="27" t="n"/>
-      <c r="L8" s="26" t="n"/>
+      <c r="L8" s="26" t="n">
+        <v>196</v>
+      </c>
       <c r="M8" s="27" t="n"/>
       <c r="N8" s="26" t="n"/>
       <c r="O8" s="27" t="n"/>
@@ -1881,9 +1889,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="28" t="n"/>
-      <c r="J9" s="26" t="n"/>
+      <c r="J9" s="26" t="n">
+        <v>172</v>
+      </c>
       <c r="K9" s="28" t="n"/>
-      <c r="L9" s="26" t="n"/>
+      <c r="L9" s="26" t="n">
+        <v>195</v>
+      </c>
       <c r="M9" s="28" t="n"/>
       <c r="N9" s="26" t="n"/>
       <c r="O9" s="28" t="n"/>
@@ -1998,9 +2010,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="28" t="n"/>
-      <c r="J10" s="26" t="n"/>
+      <c r="J10" s="26" t="n">
+        <v>160</v>
+      </c>
       <c r="K10" s="28" t="n"/>
-      <c r="L10" s="26" t="n"/>
+      <c r="L10" s="26" t="n">
+        <v>195</v>
+      </c>
       <c r="M10" s="28" t="n"/>
       <c r="N10" s="26" t="n"/>
       <c r="O10" s="28" t="n"/>
@@ -2115,9 +2131,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="28" t="n"/>
-      <c r="J11" s="26" t="n"/>
+      <c r="J11" s="26" t="n">
+        <v>160</v>
+      </c>
       <c r="K11" s="28" t="n"/>
-      <c r="L11" s="26" t="n"/>
+      <c r="L11" s="26" t="n">
+        <v>196</v>
+      </c>
       <c r="M11" s="28" t="n"/>
       <c r="N11" s="26" t="n"/>
       <c r="O11" s="28" t="n"/>
@@ -2232,9 +2252,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="28" t="n"/>
-      <c r="J12" s="26" t="n"/>
+      <c r="J12" s="26" t="n">
+        <v>160</v>
+      </c>
       <c r="K12" s="28" t="n"/>
-      <c r="L12" s="26" t="n"/>
+      <c r="L12" s="26" t="n">
+        <v>195</v>
+      </c>
       <c r="M12" s="28" t="n"/>
       <c r="N12" s="26" t="n"/>
       <c r="O12" s="28" t="n"/>
@@ -2349,9 +2373,13 @@
         <v>75</v>
       </c>
       <c r="I13" s="28" t="n"/>
-      <c r="J13" s="26" t="n"/>
+      <c r="J13" s="26" t="n">
+        <v>161</v>
+      </c>
       <c r="K13" s="28" t="n"/>
-      <c r="L13" s="26" t="n"/>
+      <c r="L13" s="26" t="n">
+        <v>195</v>
+      </c>
       <c r="M13" s="28" t="n"/>
       <c r="N13" s="26" t="n"/>
       <c r="O13" s="28" t="n"/>
@@ -2466,9 +2494,13 @@
         <v>75</v>
       </c>
       <c r="I14" s="28" t="n"/>
-      <c r="J14" s="26" t="n"/>
+      <c r="J14" s="26" t="n">
+        <v>63</v>
+      </c>
       <c r="K14" s="28" t="n"/>
-      <c r="L14" s="26" t="n"/>
+      <c r="L14" s="26" t="n">
+        <v>193</v>
+      </c>
       <c r="M14" s="28" t="n"/>
       <c r="N14" s="26" t="n"/>
       <c r="O14" s="28" t="n"/>
@@ -2583,9 +2615,13 @@
         <v>0</v>
       </c>
       <c r="I15" s="28" t="n"/>
-      <c r="J15" s="26" t="n"/>
+      <c r="J15" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="K15" s="28" t="n"/>
-      <c r="L15" s="26" t="n"/>
+      <c r="L15" s="26" t="n">
+        <v>48</v>
+      </c>
       <c r="M15" s="28" t="n"/>
       <c r="N15" s="26" t="n"/>
       <c r="O15" s="28" t="n"/>
@@ -2700,9 +2736,13 @@
         <v>0</v>
       </c>
       <c r="I16" s="28" t="n"/>
-      <c r="J16" s="26" t="n"/>
+      <c r="J16" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="K16" s="28" t="n"/>
-      <c r="L16" s="26" t="n"/>
+      <c r="L16" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" s="28" t="n"/>
       <c r="N16" s="26" t="n"/>
       <c r="O16" s="28" t="n"/>
@@ -2817,9 +2857,13 @@
         <v>0</v>
       </c>
       <c r="I17" s="28" t="n"/>
-      <c r="J17" s="26" t="n"/>
+      <c r="J17" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="K17" s="28" t="n"/>
-      <c r="L17" s="26" t="n"/>
+      <c r="L17" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" s="28" t="n"/>
       <c r="N17" s="26" t="n"/>
       <c r="O17" s="28" t="n"/>
@@ -2934,9 +2978,13 @@
         <v>0</v>
       </c>
       <c r="I18" s="28" t="n"/>
-      <c r="J18" s="26" t="n"/>
+      <c r="J18" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="K18" s="28" t="n"/>
-      <c r="L18" s="26" t="n"/>
+      <c r="L18" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" s="28" t="n"/>
       <c r="N18" s="26" t="n"/>
       <c r="O18" s="28" t="n"/>
@@ -3051,9 +3099,13 @@
         <v>0</v>
       </c>
       <c r="I19" s="28" t="n"/>
-      <c r="J19" s="26" t="n"/>
+      <c r="J19" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="K19" s="28" t="n"/>
-      <c r="L19" s="26" t="n"/>
+      <c r="L19" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" s="28" t="n"/>
       <c r="N19" s="26" t="n"/>
       <c r="O19" s="28" t="n"/>
@@ -3168,9 +3220,13 @@
         <v>0</v>
       </c>
       <c r="I20" s="28" t="n"/>
-      <c r="J20" s="26" t="n"/>
+      <c r="J20" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="K20" s="28" t="n"/>
-      <c r="L20" s="26" t="n"/>
+      <c r="L20" s="26" t="n">
+        <v>33</v>
+      </c>
       <c r="M20" s="28" t="n"/>
       <c r="N20" s="26" t="n"/>
       <c r="O20" s="28" t="n"/>
@@ -3285,9 +3341,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="28" t="n"/>
-      <c r="J21" s="26" t="n"/>
+      <c r="J21" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="K21" s="28" t="n"/>
-      <c r="L21" s="26" t="n"/>
+      <c r="L21" s="26" t="n">
+        <v>48</v>
+      </c>
       <c r="M21" s="28" t="n"/>
       <c r="N21" s="26" t="n"/>
       <c r="O21" s="28" t="n"/>
@@ -3402,9 +3462,13 @@
         <v>75</v>
       </c>
       <c r="I22" s="28" t="n"/>
-      <c r="J22" s="26" t="n"/>
+      <c r="J22" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="K22" s="28" t="n"/>
-      <c r="L22" s="26" t="n"/>
+      <c r="L22" s="26" t="n">
+        <v>173</v>
+      </c>
       <c r="M22" s="28" t="n"/>
       <c r="N22" s="26" t="n"/>
       <c r="O22" s="28" t="n"/>
@@ -3519,9 +3583,13 @@
         <v>150</v>
       </c>
       <c r="I23" s="28" t="n"/>
-      <c r="J23" s="26" t="n"/>
+      <c r="J23" s="26" t="n">
+        <v>128</v>
+      </c>
       <c r="K23" s="28" t="n"/>
-      <c r="L23" s="26" t="n"/>
+      <c r="L23" s="26" t="n">
+        <v>211</v>
+      </c>
       <c r="M23" s="28" t="n"/>
       <c r="N23" s="26" t="n"/>
       <c r="O23" s="28" t="n"/>
@@ -3636,9 +3704,13 @@
         <v>150</v>
       </c>
       <c r="I24" s="28" t="n"/>
-      <c r="J24" s="26" t="n"/>
+      <c r="J24" s="26" t="n">
+        <v>170</v>
+      </c>
       <c r="K24" s="28" t="n"/>
-      <c r="L24" s="26" t="n"/>
+      <c r="L24" s="26" t="n">
+        <v>211</v>
+      </c>
       <c r="M24" s="28" t="n"/>
       <c r="N24" s="26" t="n"/>
       <c r="O24" s="28" t="n"/>
@@ -3753,9 +3825,13 @@
         <v>150</v>
       </c>
       <c r="I25" s="28" t="n"/>
-      <c r="J25" s="26" t="n"/>
+      <c r="J25" s="26" t="n">
+        <v>170</v>
+      </c>
       <c r="K25" s="28" t="n"/>
-      <c r="L25" s="26" t="n"/>
+      <c r="L25" s="26" t="n">
+        <v>211</v>
+      </c>
       <c r="M25" s="28" t="n"/>
       <c r="N25" s="26" t="n"/>
       <c r="O25" s="28" t="n"/>
@@ -3870,9 +3946,13 @@
         <v>150</v>
       </c>
       <c r="I26" s="28" t="n"/>
-      <c r="J26" s="26" t="n"/>
+      <c r="J26" s="26" t="n">
+        <v>170</v>
+      </c>
       <c r="K26" s="28" t="n"/>
-      <c r="L26" s="26" t="n"/>
+      <c r="L26" s="26" t="n">
+        <v>212</v>
+      </c>
       <c r="M26" s="28" t="n"/>
       <c r="N26" s="26" t="n"/>
       <c r="O26" s="28" t="n"/>
@@ -3987,9 +4067,13 @@
         <v>150</v>
       </c>
       <c r="I27" s="28" t="n"/>
-      <c r="J27" s="26" t="n"/>
+      <c r="J27" s="26" t="n">
+        <v>170</v>
+      </c>
       <c r="K27" s="28" t="n"/>
-      <c r="L27" s="26" t="n"/>
+      <c r="L27" s="26" t="n">
+        <v>210</v>
+      </c>
       <c r="M27" s="28" t="n"/>
       <c r="N27" s="26" t="n"/>
       <c r="O27" s="28" t="n"/>
@@ -4104,9 +4188,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="28" t="n"/>
-      <c r="J28" s="26" t="n"/>
+      <c r="J28" s="26" t="n">
+        <v>171</v>
+      </c>
       <c r="K28" s="28" t="n"/>
-      <c r="L28" s="26" t="n"/>
+      <c r="L28" s="26" t="n">
+        <v>211</v>
+      </c>
       <c r="M28" s="28" t="n"/>
       <c r="N28" s="26" t="n"/>
       <c r="O28" s="28" t="n"/>
@@ -4221,9 +4309,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="28" t="n"/>
-      <c r="J29" s="26" t="n"/>
+      <c r="J29" s="26" t="n">
+        <v>170</v>
+      </c>
       <c r="K29" s="28" t="n"/>
-      <c r="L29" s="26" t="n"/>
+      <c r="L29" s="26" t="n">
+        <v>210</v>
+      </c>
       <c r="M29" s="28" t="n"/>
       <c r="N29" s="26" t="n"/>
       <c r="O29" s="28" t="n"/>
@@ -4338,9 +4430,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="29" t="n"/>
-      <c r="J30" s="26" t="n"/>
+      <c r="J30" s="26" t="n">
+        <v>170</v>
+      </c>
       <c r="K30" s="29" t="n"/>
-      <c r="L30" s="26" t="n"/>
+      <c r="L30" s="26" t="n">
+        <v>211</v>
+      </c>
       <c r="M30" s="29" t="n"/>
       <c r="N30" s="26" t="n"/>
       <c r="O30" s="29" t="n"/>
@@ -4457,9 +4553,13 @@
         <v>931335</v>
       </c>
       <c r="I31" s="73" t="n"/>
-      <c r="J31" s="11" t="n"/>
+      <c r="J31" s="11" t="n">
+        <v>2548748</v>
+      </c>
       <c r="K31" s="73" t="n"/>
-      <c r="L31" s="11" t="n"/>
+      <c r="L31" s="11" t="n">
+        <v>3606984</v>
+      </c>
       <c r="M31" s="73" t="n"/>
       <c r="N31" s="11" t="n"/>
       <c r="O31" s="73" t="n"/>
